--- a/src/ExcelsiorOpenXml.Tests/ComplexTypeWithSplitter.Null.verified.xlsx
+++ b/src/ExcelsiorOpenXml.Tests/ComplexTypeWithSplitter.Null.verified.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8ab390aad92741b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R053dc53173534b38"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/src/ExcelsiorOpenXml.Tests/ComplexTypeWithSplitter.Null.verified.xlsx
+++ b/src/ExcelsiorOpenXml.Tests/ComplexTypeWithSplitter.Null.verified.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R053dc53173534b38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -12,6 +12,7 @@
   <x:fonts count="1">
     <x:font>
       <x:sz val="11"/>
+      <x:name val="Aptos"/>
     </x:font>
   </x:fonts>
   <x:fills count="2">

--- a/src/ExcelsiorOpenXml.Tests/ComplexTypeWithSplitter.Null.verified.xlsx
+++ b/src/ExcelsiorOpenXml.Tests/ComplexTypeWithSplitter.Null.verified.xlsx
@@ -9,8 +9,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="1">
+  <x:fonts count="2">
     <x:font>
+      <x:sz val="11"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
       <x:sz val="11"/>
       <x:name val="Aptos"/>
     </x:font>
@@ -34,7 +39,7 @@
   </x:borders>
   <x:cellXfs count="3">
     <x:xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0"/>
-    <x:xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0"/>
+    <x:xf fontId="1" fillId="0" borderId="0" applyFont="1" applyFill="0"/>
     <x:xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyAlignment="1">
       <x:alignment horizontal="left" vertical="top" wrapText="1"/>
     </x:xf>

--- a/src/ExcelsiorOpenXml.Tests/ComplexTypeWithSplitter.Null.verified.xlsx
+++ b/src/ExcelsiorOpenXml.Tests/ComplexTypeWithSplitter.Null.verified.xlsx
@@ -12,12 +12,12 @@
   <x:fonts count="2">
     <x:font>
       <x:sz val="11"/>
-      <x:name val="Aptos"/>
+      <x:name val="Calibri"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="11"/>
-      <x:name val="Aptos"/>
+      <x:name val="Calibri"/>
     </x:font>
   </x:fonts>
   <x:fills count="2">

--- a/src/ExcelsiorOpenXml.Tests/ComplexTypeWithSplitter.Null.verified.xlsx
+++ b/src/ExcelsiorOpenXml.Tests/ComplexTypeWithSplitter.Null.verified.xlsx
@@ -9,10 +9,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="1">
+  <x:fonts count="2">
     <x:font>
       <x:sz val="11"/>
-      <x:name val="Aptos"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:name val="Calibri"/>
     </x:font>
   </x:fonts>
   <x:fills count="2">
@@ -34,7 +39,7 @@
   </x:borders>
   <x:cellXfs count="3">
     <x:xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0"/>
-    <x:xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0"/>
+    <x:xf fontId="1" fillId="0" borderId="0" applyFont="1" applyFill="0"/>
     <x:xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyAlignment="1">
       <x:alignment horizontal="left" vertical="top" wrapText="1"/>
     </x:xf>

--- a/src/ExcelsiorOpenXml.Tests/ComplexTypeWithSplitter.Null.verified.xlsx
+++ b/src/ExcelsiorOpenXml.Tests/ComplexTypeWithSplitter.Null.verified.xlsx
@@ -111,5 +111,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:autoFilter ref="A1:F2"/>
 </x:worksheet>
 </file>